--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.65754811677989</v>
+        <v>8.394351568976731</v>
       </c>
       <c r="D2" t="n">
-        <v>44.59841606460832</v>
+        <v>7.247242610498852</v>
       </c>
       <c r="E2" t="n">
-        <v>14.70441686551318</v>
+        <v>2.389467740645892</v>
       </c>
       <c r="F2" t="n">
-        <v>10.8962627206583</v>
+        <v>1.770642692106974</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.38309624038526</v>
+        <v>9.487253139062606</v>
       </c>
       <c r="D3" t="n">
-        <v>10.40607757436704</v>
+        <v>1.690987605834645</v>
       </c>
       <c r="E3" t="n">
-        <v>14.70441686551318</v>
+        <v>2.389467740645892</v>
       </c>
       <c r="F3" t="n">
-        <v>10.8962627206583</v>
+        <v>1.770642692106974</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.63861826143903</v>
+        <v>4.816275467483843</v>
       </c>
       <c r="D4" t="n">
-        <v>38.78547434131312</v>
+        <v>6.302639580463382</v>
       </c>
       <c r="E4" t="n">
-        <v>14.70441686551318</v>
+        <v>2.389467740645892</v>
       </c>
       <c r="F4" t="n">
-        <v>10.8962627206583</v>
+        <v>1.770642692106974</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>69.34671599535396</v>
+        <v>11.26884134924502</v>
       </c>
       <c r="D5" t="n">
-        <v>19.90659438477612</v>
+        <v>3.234821587526119</v>
       </c>
       <c r="E5" t="n">
-        <v>14.70441686551318</v>
+        <v>2.389467740645892</v>
       </c>
       <c r="F5" t="n">
-        <v>10.8962627206583</v>
+        <v>1.770642692106974</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.37803973853979</v>
+        <v>2.823931457512717</v>
       </c>
       <c r="D6" t="n">
-        <v>30.78394688601303</v>
+        <v>5.002391368977118</v>
       </c>
       <c r="E6" t="n">
-        <v>14.70441686551318</v>
+        <v>2.389467740645892</v>
       </c>
       <c r="F6" t="n">
-        <v>10.8962627206583</v>
+        <v>1.770642692106974</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.09467137174195</v>
+        <v>8.790384097908067</v>
       </c>
       <c r="D7" t="n">
-        <v>20.60976401863676</v>
+        <v>3.349086653028474</v>
       </c>
       <c r="E7" t="n">
-        <v>14.70441686551318</v>
+        <v>2.389467740645892</v>
       </c>
       <c r="F7" t="n">
-        <v>10.8962627206583</v>
+        <v>1.770642692106974</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>48.82610125007805</v>
+        <v>7.934241453137683</v>
       </c>
       <c r="D8" t="n">
-        <v>20.2210171669903</v>
+        <v>3.285915289635924</v>
       </c>
       <c r="E8" t="n">
-        <v>14.70441686551318</v>
+        <v>2.389467740645892</v>
       </c>
       <c r="F8" t="n">
-        <v>10.8962627206583</v>
+        <v>1.770642692106974</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>44.17177506012931</v>
+        <v>7.177913447271013</v>
       </c>
       <c r="D9" t="n">
-        <v>22.50178632394212</v>
+        <v>3.656540277640595</v>
       </c>
       <c r="E9" t="n">
-        <v>14.70441686551318</v>
+        <v>2.389467740645892</v>
       </c>
       <c r="F9" t="n">
-        <v>10.8962627206583</v>
+        <v>1.770642692106974</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.68967418559629</v>
+        <v>4.662072055159396</v>
       </c>
       <c r="D10" t="n">
-        <v>35.09583884029432</v>
+        <v>5.703073811547827</v>
       </c>
       <c r="E10" t="n">
-        <v>14.70441686551318</v>
+        <v>2.389467740645892</v>
       </c>
       <c r="F10" t="n">
-        <v>10.8962627206583</v>
+        <v>1.770642692106974</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.07478564580514</v>
+        <v>5.537152667443336</v>
       </c>
       <c r="D11" t="n">
-        <v>38.55258744929881</v>
+        <v>6.264795460511057</v>
       </c>
       <c r="E11" t="n">
-        <v>14.70441686551318</v>
+        <v>2.389467740645892</v>
       </c>
       <c r="F11" t="n">
-        <v>10.8962627206583</v>
+        <v>1.770642692106974</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.86648450773268</v>
+        <v>5.34080373250656</v>
       </c>
       <c r="D12" t="n">
-        <v>37.74853439452879</v>
+        <v>6.134136839110928</v>
       </c>
       <c r="E12" t="n">
-        <v>14.70441686551318</v>
+        <v>2.389467740645892</v>
       </c>
       <c r="F12" t="n">
-        <v>10.8962627206583</v>
+        <v>1.770642692106974</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>57.77313975371032</v>
+        <v>9.388135209977928</v>
       </c>
       <c r="D13" t="n">
-        <v>45.84221340943515</v>
+        <v>7.449359679033213</v>
       </c>
       <c r="E13" t="n">
-        <v>14.70441686551318</v>
+        <v>2.389467740645892</v>
       </c>
       <c r="F13" t="n">
-        <v>10.8962627206583</v>
+        <v>1.770642692106974</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
